--- a/data/radio-channels.xlsx
+++ b/data/radio-channels.xlsx
@@ -229,8 +229,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RadioChannels" displayName="RadioChannels" ref="A5:I23" headerRowCount="1" totalsRowShown="0">
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RadioChannels" displayName="RadioChannels" ref="A5:J26" headerRowCount="1" totalsRowShown="0">
+  <tableColumns count="10">
     <tableColumn id="1" name="No."/>
     <tableColumn id="2" name="Channel / الإذاعة"/>
     <tableColumn id="3" name="Stream URL — EDIT HERE"/>
@@ -240,6 +240,7 @@
     <tableColumn id="7" name="Favourite"/>
     <tableColumn id="8" name="Source page"/>
     <tableColumn id="9" name="Notes"/>
+    <tableColumn id="10" name="Show / إظهار"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -445,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -457,6 +458,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="56" customWidth="1" min="8" max="8"/>
     <col width="69" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -557,6 +559,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Show / إظهار</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="32.1" customHeight="1">
       <c r="A6" s="5" t="n">
@@ -600,6 +607,11 @@
           <t>Audio data received; listening not tested.</t>
         </is>
       </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="32.1" customHeight="1">
       <c r="A7" s="4" t="n">
@@ -638,7 +650,12 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>User-provided URL; signed link may expire. Playback not checked.</t>
+          <t>User-provided URL; signed link may expire. Playback not checked. — Hidden 22/10/2026: Maspero publishes it only via Dailymotion; signed links expire within hours.</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -679,7 +696,12 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Updated with user-provided URL on 21/10/2026; signed link may expire.</t>
+          <t>Updated with user-provided URL on 21/10/2026; signed link may expire. — Hidden 22/10/2026: Maspero publishes it only via Dailymotion; signed links expire within hours.</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -725,6 +747,11 @@
           <t>Audio data received; listening not tested.</t>
         </is>
       </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="32.1" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -768,6 +795,11 @@
           <t>Directory attribution; stream metadata says No Name.</t>
         </is>
       </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="32.1" customHeight="1">
       <c r="A11" s="5" t="n">
@@ -811,6 +843,11 @@
           <t>Audio data received; listening not tested.</t>
         </is>
       </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="32.1" customHeight="1">
       <c r="A12" s="4" t="n">
@@ -854,6 +891,11 @@
           <t>Audio data received; listening not tested.</t>
         </is>
       </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="32.1" customHeight="1">
       <c r="A13" s="5" t="n">
@@ -897,6 +939,11 @@
           <t>Audio data received; listening not tested.</t>
         </is>
       </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="32.1" customHeight="1">
       <c r="A14" s="4" t="n">
@@ -933,7 +980,12 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>No verified direct URL; video ID x8n6dqq. Searched 21/10/2026; no working direct URL verified.</t>
+          <t>No verified direct URL; video ID x8n6dqq. Searched 21/10/2026; no working direct URL verified. — Hidden 22/10/2026: Maspero publishes it only via Dailymotion; signed links expire within hours.</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -972,7 +1024,12 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>No verified direct URL; video ID x8n6drt. Searched 21/10/2026; no working direct URL verified.</t>
+          <t>No verified direct URL; video ID x8n6drt. Searched 21/10/2026; no working direct URL verified. — Hidden 22/10/2026: Maspero publishes it only via Dailymotion; signed links expire within hours.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1068,12 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>No verified direct URL; video ID x8n6eci. Searched 21/10/2026; no working direct URL verified.</t>
+          <t>No verified direct URL; video ID x8n6eci. Searched 21/10/2026; no working direct URL verified. — Hidden 22/10/2026: Maspero publishes it only via Dailymotion; signed links expire within hours.</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1057,6 +1119,11 @@
           <t>Official page embeds this source; metadata: Nogoum FM. Audio received; listening not tested.</t>
         </is>
       </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="32.1" customHeight="1">
       <c r="A18" s="5" t="n">
@@ -1100,6 +1167,11 @@
           <t>Metadata: Radio Hits. Audio received; listening not tested.</t>
         </is>
       </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="32.1" customHeight="1">
       <c r="A19" s="4" t="n">
@@ -1143,6 +1215,11 @@
           <t>Directory attribution; audio received. Station identity not confirmed by listening.</t>
         </is>
       </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="4" t="n">
@@ -1187,8 +1264,13 @@
           <t>Sheikh Al-Sha'rawi tafsir radio (quran-uni.com). Second line = backup server listed on e-quran.com/pages/radio/imam-al-sharawi.html.</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="32.1" customHeight="1">
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
       <c r="A21" s="4" t="n">
         <v>20</v>
       </c>
@@ -1197,9 +1279,10 @@
           <t>إذاعة المنشاوي</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>https://backup.qurango.net/radio/mohammed_siddiq_alminshawi</t>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>https://backup.qurango.net/radio/mohammed_siddiq_alminshawi
+https://serverkw.quran-uni.com:8074/;*.mp3</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1227,7 +1310,12 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Mohamed Siddiq Al-Minshawi — murattal, 24/7 (mp3quran.net).</t>
+          <t>Murattal, 24/7. Line 1: mp3quran.net; line 2 (backup): quran-uni.com Minshawi radio (Hafs, murattal).</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1273,6 +1361,11 @@
           <t>Mohamed Siddiq Al-Minshawi — mujawwad, 24/7 (mp3quran.net).</t>
         </is>
       </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="32.1" customHeight="1">
       <c r="A23" s="4" t="n">
@@ -1305,7 +1398,156 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Tribute stations exist (Morocco: oumkalthoumradio.ma; Zeno.FM) but no stream URL could be verified. In the app: station page → find stream (searches all countries). Paste a URL here when you have one.</t>
+          <t>No fixed link: the app finds and plays an Umm Kulthum listing automatically (e.g. Radio Oum Kalthoum, MAP Morocco). Paste a URL here to pin one.</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32.1" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>إذاعة الحصري</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>https://backup.qurango.net/radio/mahmoud_khalil_alhussary</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>MP3</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Listed in mp3quran.net radio API / not checked</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>46317</v>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>https://mp3quran.net/api/v3/radios?language=ar</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Mahmoud Khalil Al-Husary — murattal, 24/7.</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32.1" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>إذاعة الحصري مجود</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>https://backup.qurango.net/radio/mahmoud_khalil_alhussary_mojawwad</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>MP3</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Listed in mp3quran.net radio API / not checked</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>46317</v>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>https://mp3quran.net/api/v3/radios?language=ar</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Mahmoud Khalil Al-Husary — mujawwad, 24/7.</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32.1" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>إذاعة مصطفى إسماعيل</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>https://backup.qurango.net/radio/mustafa_ismail</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>MP3</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Listed in mp3quran.net radio API / not checked</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>46317</v>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>https://mp3quran.net/api/v3/radios?language=ar</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Mustafa Ismail, 24/7 (mp3quran.net has one Mustafa Ismail radio; no separate murattal/mujawwad radios exist there).</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/data/radio-channels.xlsx
+++ b/data/radio-channels.xlsx
@@ -229,7 +229,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RadioChannels" displayName="RadioChannels" ref="A5:J26" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RadioChannels" displayName="RadioChannels" ref="A5:J27" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="10">
     <tableColumn id="1" name="No."/>
     <tableColumn id="2" name="Channel / الإذاعة"/>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1542,10 +1542,58 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Mustafa Ismail, 24/7 (mp3quran.net has one Mustafa Ismail radio; no separate murattal/mujawwad radios exist there).</t>
+          <t>Mustafa Ismail live radio (mp3quran.net; recitation style not stated by the source). For tajweed see the next row.</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32.1" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>إذاعة مصطفى إسماعيل تجويد</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>https://cdn.mp3quran.net/audio/mustafa-ismail/r2/</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Playlist (114 سورة)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>mp3quran.net المصحف المجود (moshaf 288, 114 surahs) / not checked</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>46317</v>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>https://mp3quran.net/api/v3/reciters?language=ar</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Mustafa Ismail — المصحف المجود. No live tajweed radio exists; the app plays the surah files 001–114 in order, starting at a random surah, looping. Format "Playlist" = folder of surah files.</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/data/radio-channels.xlsx
+++ b/data/radio-channels.xlsx
@@ -229,7 +229,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RadioChannels" displayName="RadioChannels" ref="A5:J27" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RadioChannels" displayName="RadioChannels" ref="A5:J28" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="10">
     <tableColumn id="1" name="No."/>
     <tableColumn id="2" name="Channel / الإذاعة"/>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1599,6 +1599,55 @@
         </is>
       </c>
     </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>مصطفى إسماعيل تسجيلات نادرة</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/Torath_Mustafa_Ismaiil_By_ReDa_MoHamMeD
+https://archive.org/details/way2sona_20160405_2121</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Internet Archive collections / not checked</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>46317</v>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>https://archive.org/details/Torath_Mustafa_Ismaiil_By_ReDa_MoHamMeD</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Rare tajweed: concerts &amp; external recordings (1191, uploaded by Reda Mohammed) + 50 rare high-quality recordings. Shuffled like a radio; Next on the lock screen skips to another recording. Format "Archive ordered" keeps the order. Add more archive.org/details links (one per line).</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="E6:E19">
     <cfRule type="containsText" priority="1" operator="containsText" dxfId="1" text="Needs"/>

--- a/data/radio-channels.xlsx
+++ b/data/radio-channels.xlsx
@@ -15,9 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="7">
     <font>
       <name val="Carlito"/>
@@ -1261,12 +1259,12 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Sheikh Al-Sha'rawi tafsir radio (quran-uni.com). Second line = backup server listed on e-quran.com/pages/radio/imam-al-sharawi.html.</t>
+          <t>Sheikh Al-Sha'rawi tafsir radio (quran-uni.com). Second line = backup server listed on e-quran.com/pages/radio/imam-al-sharawi.html. — 27/10/2026: moved into its own section (Show = Section): not listed with radio stations; plays from the Tafsir page.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Section</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1396,12 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>No fixed link: the app finds and plays an Umm Kulthum listing automatically (e.g. Radio Oum Kalthoum, MAP Morocco). Paste a URL here to pin one.</t>
+          <t>No fixed link: the app finds and plays an Umm Kulthum listing automatically (e.g. Radio Oum Kalthoum, MAP Morocco). Paste a URL here to pin one. — 27/10/2026: moved into its own section (Show = Section): not listed with radio stations; plays from the Umm Kulthum page.</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Section</t>
         </is>
       </c>
     </row>
